--- a/utils/monday_sprint_sprint_2024-51.xlsx
+++ b/utils/monday_sprint_sprint_2024-51.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="183">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>28982</t>
+    <t>8001973024</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>06/12/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>19/12/2024</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,19 +102,19 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>27379</t>
+    <t>8002397747</t>
   </si>
   <si>
     <t>Interface Planilhas Custeio Gerencial x Sistema de Custeio</t>
   </si>
   <si>
+    <t>11/12/2024</t>
+  </si>
+  <si>
     <t>Impedimento</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>28956</t>
+    <t>8014456792</t>
   </si>
   <si>
     <t>PDI_RespostaNew – A sequência que apresentar laudo ‘Analisar’ ou ‘Retrabalho’ criar nova PDI.</t>
@@ -123,6 +123,9 @@
     <t>09/12/2024</t>
   </si>
   <si>
+    <t>08/12/2024</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
@@ -150,7 +153,7 @@
     <t>Semana 3</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>8009669158</t>
   </si>
   <si>
     <t>Geração dos registros K230 e K235</t>
@@ -159,124 +162,133 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>8019050535</t>
+  </si>
+  <si>
     <t>Ajuste no sistema BLOCO K</t>
   </si>
   <si>
     <t>10/12/2024</t>
   </si>
   <si>
+    <t>17/12/2024</t>
+  </si>
+  <si>
     <t>Testes</t>
   </si>
   <si>
-    <t>29095</t>
+    <t>8001618352</t>
   </si>
   <si>
     <t>Apontamento Ajustagem</t>
   </si>
   <si>
-    <t>29025</t>
+    <t>8001842419</t>
   </si>
   <si>
     <t>Melhoria aplicação do orçamento</t>
   </si>
   <si>
-    <t>29117</t>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>8001529673</t>
   </si>
   <si>
     <t>Melhoria no sistema visual da cadeia de ajuda komatsu</t>
   </si>
   <si>
-    <t>29127</t>
+    <t>8012495255</t>
   </si>
   <si>
     <t>Melhorias sistema de pré-lista</t>
   </si>
   <si>
-    <t>29115</t>
+    <t>8001543592</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Nimbi X Imobilizado</t>
   </si>
   <si>
-    <t>29109</t>
+    <t>8001560566</t>
   </si>
   <si>
     <t>Lançamento de dados CPP retroativos para BI IROG Inspeção</t>
   </si>
   <si>
-    <t>29086</t>
+    <t>8001635055</t>
   </si>
   <si>
     <t>Retorno Usinagem</t>
   </si>
   <si>
-    <t>29129</t>
+    <t>8001490101</t>
   </si>
   <si>
     <t>BLOQUEIO DE SISTEMA 12/12/2024 - INVENTÁRIO ALMOXARIFADO</t>
   </si>
   <si>
-    <t>29053</t>
+    <t>8001700045</t>
   </si>
   <si>
     <t>CONSULTA CPP FLUXOS DE ANÁLISE CRÍTICA</t>
   </si>
   <si>
-    <t>29105</t>
+    <t>8001609325</t>
   </si>
   <si>
     <t>Atualização no sistema de desmoldagem</t>
   </si>
   <si>
-    <t>29077</t>
+    <t>8001663047</t>
   </si>
   <si>
     <t>Alterar o setor para o nome</t>
   </si>
   <si>
-    <t>27474</t>
+    <t>8009536975</t>
   </si>
   <si>
     <t>Indicar com setas e botões para mudar de página.</t>
   </si>
   <si>
-    <t>29014</t>
+    <t>8001859596</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO FLUXO 104</t>
   </si>
   <si>
-    <t>29004</t>
+    <t>8001904879</t>
   </si>
   <si>
     <t>Dados de Bolo e Moldagem</t>
   </si>
   <si>
-    <t>26964</t>
+    <t>8009536800</t>
   </si>
   <si>
     <t>Executar chamado para criação de indicadores de controle de leitura de documentos</t>
   </si>
   <si>
-    <t>28065</t>
+    <t>8001995761</t>
   </si>
   <si>
     <t>Avaliação Ronda</t>
   </si>
   <si>
-    <t>29061</t>
+    <t>8001677701</t>
   </si>
   <si>
     <t>Alteração no sistema SMI</t>
   </si>
   <si>
-    <t>28984</t>
+    <t>8001949319</t>
   </si>
   <si>
     <t>CAMPO DE DESENHO DE FORNECIMENTO</t>
   </si>
   <si>
-    <t>29272</t>
+    <t>8067504284</t>
   </si>
   <si>
     <t>Correção</t>
@@ -285,22 +297,19 @@
     <t>(B.I. Inspeção)</t>
   </si>
   <si>
-    <t>17/12/2024</t>
-  </si>
-  <si>
-    <t>29107</t>
+    <t>8001580554</t>
   </si>
   <si>
     <t>MPO Esmerilhadeiras e Retíficas - Ajustagem</t>
   </si>
   <si>
-    <t>29001</t>
+    <t>8009788458</t>
   </si>
   <si>
     <t>ERRO SALDO 108892/93</t>
   </si>
   <si>
-    <t>28847</t>
+    <t>8009591584</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -309,19 +318,22 @@
     <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento</t>
   </si>
   <si>
-    <t>28800</t>
+    <t>8009536846</t>
   </si>
   <si>
     <t>INCLUSÃO DE OTFs PARCIAIS</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>8010091510</t>
   </si>
   <si>
     <t>Habilitar Tela eventos financeiros para Sueli - Julius</t>
   </si>
   <si>
-    <t>28135</t>
+    <t>12/12/2024</t>
+  </si>
+  <si>
+    <t>8094964147</t>
   </si>
   <si>
     <t>Apontamento de moldagem USE - Máquina</t>
@@ -330,28 +342,34 @@
     <t>20/12/2024</t>
   </si>
   <si>
-    <t>28686</t>
+    <t>8009536888</t>
   </si>
   <si>
     <t>Ciclo de indicadores com Ano comercial</t>
   </si>
   <si>
+    <t>8009624874</t>
+  </si>
+  <si>
     <t>Controle de Eventos Financeiros - Verificar cobrança conforme alocação</t>
   </si>
   <si>
+    <t>8045600796</t>
+  </si>
+  <si>
     <t>Consulta do campo “Setor do fluxo SPS”</t>
   </si>
   <si>
     <t>13/12/2024</t>
   </si>
   <si>
-    <t>29051</t>
+    <t>8001714790</t>
   </si>
   <si>
     <t>ANÁLISES CRÍTICAS PARCIAIS</t>
   </si>
   <si>
-    <t>29032</t>
+    <t>8001729166</t>
   </si>
   <si>
     <t>Projeto - Sequencias Críticas</t>
@@ -360,55 +378,79 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>28316</t>
+    <t>8009788406</t>
   </si>
   <si>
     <t>Movimentação da montagem do conjunto das Tampas</t>
   </si>
   <si>
-    <t>29132</t>
+    <t>8002028608</t>
   </si>
   <si>
     <t>Melhorias sistema Ronda</t>
   </si>
   <si>
+    <t>18/12/2024</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
+    <t>8045344937</t>
+  </si>
+  <si>
     <t>Gerar registro no Benner</t>
   </si>
   <si>
+    <t>8014449379</t>
+  </si>
+  <si>
     <t>WWPDI_Inspeção – Ordenar Grid / Manter os filtros</t>
   </si>
   <si>
+    <t>8014453046</t>
+  </si>
+  <si>
     <t>PDI_RespostaNew – Identificar quem fez o apontamento (inspetor ou analista/engenheiro).</t>
   </si>
   <si>
+    <t>8014454330</t>
+  </si>
+  <si>
     <t>PDI_RespostaNew – Coluna laudo, disponibilizar opção conforme tipo (inspetor ou analista/engenheiro).</t>
   </si>
   <si>
+    <t>8009578169</t>
+  </si>
+  <si>
     <t>Consulta de indicadores sem plano de ação cadastrado, com opção de disparar e-mail para os responsáveis  - Calendário Comercial</t>
   </si>
   <si>
+    <t>8014455668</t>
+  </si>
+  <si>
     <t>PDI_RespostaNew – Criar funcionalidade para finalizar o apontamento das cotas.</t>
   </si>
   <si>
+    <t>8009585110</t>
+  </si>
+  <si>
     <t>Consulta de indicadores sem plano de ação cadastrado, com opção de disparar e-mail para os responsáveis  - Calendário Comercial  com gráficos e consultas</t>
   </si>
   <si>
-    <t>28798</t>
+    <t>8009536930</t>
   </si>
   <si>
     <t>Cenário Valorização 2</t>
   </si>
   <si>
-    <t>27746</t>
+    <t>8009541978</t>
   </si>
   <si>
     <t>Relatório de Recibo de Embarque - Vinculo NF x Sequencia</t>
   </si>
   <si>
-    <t>26389</t>
+    <t>7942616814</t>
   </si>
   <si>
     <t>Controle Automático de n° sequencial de peça para ID de Bruto</t>
@@ -423,25 +465,25 @@
     <t>Novembro</t>
   </si>
   <si>
-    <t>29138</t>
+    <t>8071606854</t>
   </si>
   <si>
     <t>Cálculo NF de importação</t>
   </si>
   <si>
-    <t>29119</t>
+    <t>8001513173</t>
   </si>
   <si>
     <t>Atualização WMS - Rotas e Locais</t>
   </si>
   <si>
-    <t>29124</t>
+    <t>8001500875</t>
   </si>
   <si>
     <t>Inventário Avulso WMS</t>
   </si>
   <si>
-    <t>28993</t>
+    <t>8001923032</t>
   </si>
   <si>
     <t>Gerar Estrutura de Dados</t>
@@ -453,7 +495,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-51</t>
+    <t>Nov/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -502,9 +544,6 @@
   </si>
   <si>
     <t>Muito Alta</t>
-  </si>
-  <si>
-    <t>Sim</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1083,13 +1122,13 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1130,16 +1169,16 @@
         <v>35</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1147,25 +1186,25 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1174,19 +1213,19 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>28</v>
@@ -1194,7 +1233,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1206,13 +1245,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1224,16 +1263,16 @@
         <v>35</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1241,7 +1280,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1253,10 +1292,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1268,19 +1307,19 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1288,7 +1327,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1300,10 +1339,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1318,7 +1357,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1335,7 +1374,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1347,10 +1386,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1365,13 +1404,13 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1382,7 +1421,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1394,10 +1433,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1412,13 +1451,13 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1429,7 +1468,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1441,10 +1480,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1459,16 +1498,16 @@
         <v>35</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1476,7 +1515,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1488,13 +1527,13 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>21</v>
@@ -1506,13 +1545,13 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>27</v>
@@ -1523,7 +1562,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1535,10 +1574,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1570,7 +1609,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1582,10 +1621,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1617,7 +1656,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1629,10 +1668,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1647,13 +1686,13 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -1664,7 +1703,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1676,10 +1715,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1694,7 +1733,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1711,7 +1750,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1723,10 +1762,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1758,7 +1797,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1770,10 +1809,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1805,7 +1844,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1817,10 +1856,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1835,7 +1874,7 @@
         <v>35</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1844,7 +1883,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1852,7 +1891,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1864,10 +1903,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1899,7 +1938,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1911,10 +1950,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -1946,7 +1985,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1958,10 +1997,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1976,7 +2015,7 @@
         <v>35</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1985,7 +2024,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -1993,7 +2032,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2005,10 +2044,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2023,7 +2062,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2040,7 +2079,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2052,10 +2091,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2070,7 +2109,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2087,7 +2126,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2099,10 +2138,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2117,7 +2156,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2134,22 +2173,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2161,7 +2200,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2173,7 +2212,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2181,7 +2220,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2193,10 +2232,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2211,13 +2250,13 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>27</v>
@@ -2228,22 +2267,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2258,16 +2297,16 @@
         <v>35</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2275,22 +2314,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2305,16 +2344,16 @@
         <v>35</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2322,7 +2361,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2334,10 +2373,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2361,7 +2400,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2369,25 +2408,25 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2399,7 +2438,7 @@
         <v>35</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2408,7 +2447,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2416,7 +2455,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2428,13 +2467,13 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -2443,7 +2482,7 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>24</v>
@@ -2455,7 +2494,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2463,7 +2502,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2475,10 +2514,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2493,7 +2532,7 @@
         <v>35</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2502,7 +2541,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2510,22 +2549,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2540,7 +2579,7 @@
         <v>35</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2549,7 +2588,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2557,7 +2596,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2569,10 +2608,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2584,7 +2623,7 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>24</v>
@@ -2596,7 +2635,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>28</v>
@@ -2604,7 +2643,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2616,10 +2655,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2634,13 +2673,13 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>27</v>
@@ -2651,7 +2690,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2663,10 +2702,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2681,10 +2720,10 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>26</v>
@@ -2698,7 +2737,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2710,10 +2749,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2728,16 +2767,16 @@
         <v>35</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>28</v>
@@ -2745,7 +2784,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2757,10 +2796,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2775,13 +2814,13 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>27</v>
@@ -2792,7 +2831,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2804,10 +2843,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2819,19 +2858,19 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -2839,7 +2878,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2851,10 +2890,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2869,16 +2908,16 @@
         <v>35</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -2886,7 +2925,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2898,10 +2937,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -2916,16 +2955,16 @@
         <v>35</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>28</v>
@@ -2933,7 +2972,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -2945,10 +2984,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2963,7 +3002,7 @@
         <v>35</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -2972,7 +3011,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>28</v>
@@ -2980,7 +3019,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -2992,10 +3031,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3010,7 +3049,7 @@
         <v>35</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3019,7 +3058,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>28</v>
@@ -3027,7 +3066,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3039,10 +3078,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3057,7 +3096,7 @@
         <v>35</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3066,7 +3105,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3074,7 +3113,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3086,10 +3125,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3104,7 +3143,7 @@
         <v>35</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3113,7 +3152,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3121,7 +3160,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3133,10 +3172,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3151,16 +3190,16 @@
         <v>35</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3168,7 +3207,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3180,10 +3219,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3198,16 +3237,16 @@
         <v>35</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3215,7 +3254,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3227,10 +3266,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3242,27 +3281,27 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3274,10 +3313,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3289,10 +3328,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3301,7 +3340,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3309,7 +3348,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3321,10 +3360,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3339,7 +3378,7 @@
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3356,7 +3395,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3368,10 +3407,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3386,10 +3425,10 @@
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>26</v>
@@ -3403,7 +3442,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3415,10 +3454,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3433,10 +3472,10 @@
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>26</v>
@@ -3461,23 +3500,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3485,16 +3524,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3502,10 +3541,10 @@
         <v>52</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -3513,7 +3552,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3526,7 +3565,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -3534,7 +3573,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3565,12 +3604,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B2">
         <v>52</v>
@@ -3578,13 +3617,13 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3594,25 +3633,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3629,16 +3668,16 @@
         <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>163</v>
+        <v>58</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -3647,21 +3686,21 @@
         <v>33</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H11">
         <v>4</v>
@@ -3670,24 +3709,24 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="M11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N11">
         <v>7</v>
       </c>
       <c r="P11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="Q11">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3699,39 +3738,33 @@
         <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="K12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
-      <c r="P12" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -3739,13 +3772,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -3753,7 +3786,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3761,7 +3794,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3769,7 +3802,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -3777,10 +3810,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3788,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3796,142 +3829,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
